--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Cashiering › Receive Payment; Cashiering › Receipts; Cashiering › Unapplied Payments; Cashiering › Incoming Requests; Cashiering › Pre-booked Payments; Cashiering › Payment Uploads; Cashiering › PDC Warehouse; Cashiering › Batch Print; Cashiering › Commission ORs; Cashiering › Receipt Series; Cashiering › Cashiering Setup; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Cashiering › Create AR/OR; Cashiering › Posting; Cashiering › Receive Payment; Cashiering › Receipts; Cashiering › Unapplied Payments; Cashiering › Unapplied Payment List; Cashiering › Day-End List; Cashiering › Search Log; Cashiering › Incoming Requests; Cashiering › Pre-booked Payments; Cashiering › Payment Uploads; Cashiering › Payment Files; Cashiering › PDC Warehouse; Cashiering › Batch Print; Cashiering › Commission ORs; Cashiering › Settlement ORs; Cashiering › AR and OR Forms; Cashiering › Receipt Series; Cashiering › Cashiering Setup; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Cashiering › Receive Payment; Cashiering › Receipts; Cashiering › Unapplied Payments; Cashiering › Incoming Requests; Cashiering › Pre-booked Payments; Cashiering › Payment Uploads; Cashiering › PDC Warehouse; Cashiering › Batch Print; Cashiering › Commission ORs; Cashiering › Receipt Series; Cashiering › Cashiering Setup; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Cashiering › Create AR/OR; Cashiering › Posting; Cashiering › Receive Payment; Cashiering › Receipts; Cashiering › Unapplied Payments; Cashiering › Unapplied Payment List; Cashiering › Day-End List; Cashiering › Search Log; Cashiering › Incoming Requests; Cashiering › Pre-booked Payments; Cashiering › Payment Uploads; Cashiering › Payment Files; Cashiering › PDC Warehouse; Cashiering › Batch Print; Cashiering › Commission ORs; Cashiering › Settlement ORs; Cashiering › AR and OR Forms; Cashiering › Receipt Series; Cashiering › Cashiering Setup; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Cashiering › Receive Payment; Cashiering › Receipts; Cashiering › Unapplied Payments; Cashiering › Incoming Requests; Cashiering › Pre-booked Payments; Cashiering › Payment Uploads; Cashiering › PDC Warehouse; Cashiering › Batch Print; Cashiering › Commission ORs; Cashiering › Receipt Series; Cashiering › Cashiering Setup; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Cashiering › Create AR/OR; Cashiering › Posting; Cashiering › Receive Payment; Cashiering › Receipts; Cashiering › Unapplied Payments; Cashiering › Unapplied Payment List; Cashiering › Day-End List; Cashiering › Search Log; Cashiering › Incoming Requests; Cashiering › Pre-booked Payments; Cashiering › Payment Uploads; Cashiering › Payment Files; Cashiering › PDC Warehouse; Cashiering › Batch Print; Cashiering › Commission ORs; Cashiering › Settlement ORs; Cashiering › AR and OR Forms; Cashiering › Receipt Series; Cashiering › Cashiering Setup; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Cashiering Workbench; Cashiering › Unapplied Payment List; Cashiering › Search Log; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Search Log; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Operations › Operations › Disbursement Queue; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Search Log; Operations › Operations › Disbursement Queue; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Search Log; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Operations › Operations › Interfaces; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Search Log; Operations › Operations › Interfaces; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
+          <t>Operations › Operations › Operations Home; Operations › Operations › Invoice Search; Cashiering › Search Log; Operations › Operations › Report Archive; Reports › Reports › Report Centre; Operations › Operations › Notification Settings</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Invoice Search (E.15)</t>
+          <t>Invoice Search (E.24)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Receive Payment (E.2)</t>
+          <t>Receive Payment (E.5)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Receipt (E.4)</t>
+          <t>Receipt (E.7)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Unapplied Payment (E.6)</t>
+          <t>Unapplied Payment (E.9)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Unapplied Payment (E.6)</t>
+          <t>Unapplied Payment (E.9)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Receipt (E.4)</t>
+          <t>Receipt (E.7)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Receipt (E.4)</t>
+          <t>Receipt (E.7)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Receipt Series (E.13)</t>
+          <t>Receipt Series (E.20)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Payment Uploads (E.9)</t>
+          <t>Payment Uploads (E.13)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Pre-booked Payments (E.8)</t>
+          <t>Pre-booked Payments (E.12)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>PDC Warehouse (E.10)</t>
+          <t>PDC Warehouse (E.15)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Unapplied Payments (E.5)</t>
+          <t>Unapplied Payments (E.8)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Unapplied Payment (E.6)</t>
+          <t>Unapplied Payment (E.9)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Receipts (E.3)</t>
+          <t>Receipts (E.6)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Receive Payment (E.2)</t>
+          <t>Receive Payment (E.5)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Batch Print (E.11)</t>
+          <t>Batch Print (E.16)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Report Centre (Operations reports) (E.18)</t>
+          <t>Report Centre (Operations reports) (E.27)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Report (E.19)</t>
+          <t>Report (E.28)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -384,6 +384,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -409,6 +412,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -705,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,13 +721,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -750,6 +759,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -822,6 +832,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -867,7 +878,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>BIBS UAT environment (address issued with the passwords). Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -889,6 +900,7 @@
         <v>21</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -920,13 +932,15 @@
       </c>
       <c r="C27" s="16" t="inlineStr"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Environment: BIBS UAT environment (address issued with the passwords). Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
-        </is>
-      </c>
-    </row>
+          <t>Environment: BIBS UAT environment: https://uat.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -984,6 +998,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1383,7 +1398,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>BIBS UAT environment (address issued with the passwords). Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -384,9 +384,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -412,9 +409,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -711,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="B4:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -721,16 +715,13 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
-    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -759,7 +750,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -832,7 +822,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -900,7 +889,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -932,7 +920,6 @@
       </c>
       <c r="C27" s="16" t="inlineStr"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
@@ -940,7 +927,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -998,7 +984,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS DEV environment: https://dev.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -923,7 +923,7 @@
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Environment: BIBS UAT environment: https://uat.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
+          <t>Environment: BIBS DEV environment: https://dev.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS DEV environment: https://dev.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,13 +715,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -750,6 +753,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -822,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -889,6 +894,7 @@
         <v>21</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -920,6 +926,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
@@ -927,6 +934,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -984,6 +992,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -952,7 +952,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1351,7 +1351,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2046,7 +2046,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3137,7 +3137,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3199,7 +3199,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_UAT_BRD-02_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -2044,7 +2044,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
